--- a/Översikt AVESTA.xlsx
+++ b/Översikt AVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>46059</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45254</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45103</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44699</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>46042</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45257</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45240</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>44531</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>45643</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44574</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45562</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>46246</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>45817</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46059</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44643</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45243</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45370</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45889</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>46035</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>45569</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>45961</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>45628</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>45995</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45190</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>46183</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>46108</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>46244</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>44574</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>46239</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45804</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45863</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45863</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>45758</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45952</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>45995</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>46056</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>44467</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>44722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44747</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44477</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>44832</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>44575</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>44747</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>44512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>45252</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>44963</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45267</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>44967</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>45082</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>45510</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45008</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>45265</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>45123</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>45123</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>45314</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>45019</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>45496</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>45583</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>45583</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45138</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>44855</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>45447</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>44614</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>44684</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>45598</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>45598</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>45560</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44809</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>45269</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45751</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45040</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45499</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>44746</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45257</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45348</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44753</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>45058</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>45496</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>45496</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44980</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>45721</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>45492</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>45583</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>44865</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>44687</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>44460</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>45196</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45196</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44587</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>45328</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>45446</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>45915</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45611</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         <v>44746</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>45511</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>45007</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>45162</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>45684</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>45910</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>45527</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>45884</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45602</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45897</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45897</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45897</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45370</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>45897</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45897</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>45903</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45791</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45910</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45911</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45008</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>45007</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>45505</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>44971</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>46141</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45138</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>45919</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>45922</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>45721</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45496</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>45457</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45929</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45321</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>45044</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>46146</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>45936</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>46146</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>45269</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>45937</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>45937</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>44977</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>45628</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>45007</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>45943</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>45902</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>45944</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>45729</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45948</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45948</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45951</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45954</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>44972</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>45736</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45800</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>45719</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>46134</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>45453</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>45912</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>46155</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>45973</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>45803</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>45497</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>45694</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>45792</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45734</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>45040</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45370</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>46155</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>46155</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45982</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>44581</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45715</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45441</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45769</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>45791</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>45058</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>45455</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>46055</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45072</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>45330</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>44876</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>45232</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45994</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45274</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45649</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45702</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44839</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>45999</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>46000</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45505</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>44551</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>44966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>45210</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44971</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45182</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44893</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>46169</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>46169</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>46169</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44734</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>46021</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>45967</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>45009</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45009</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>46042</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>46045</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>46049</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>46049</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>46049</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>46175</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>46055</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>46178</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45792</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>46124</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>46034</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45015</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>46062</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45191</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>46071</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>46184</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>46183</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>44739</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>45231</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>46185</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>44900</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>46013</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45058</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>45583</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>45583</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45549</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>46196</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>46198</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>46198</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>46198</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>46111</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>46113</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>46113</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>46113</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>46113</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>46113</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>46113</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>46244</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>44613</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45273</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>46128</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>46128</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>46128</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>46128</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>44840</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>46135</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20584,7 +20584,7 @@
         <v>45266</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>46133</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>45190</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45473</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>45866</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>45408</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45369</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44875</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>46246</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>45008</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45763</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45316</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>46205</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46252</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45602</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44739</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45538</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45625</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45646</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45264</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45078</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>46265</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45123</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>46261</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>46223</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45562</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45721</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45103</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45453</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>45639</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45777</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45369</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>46168</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>45405</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>46275</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45553</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>45510</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45316</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>44998</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45796</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45405</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>45238</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45702</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>45796</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>45796</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45796</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>46283</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>45656</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45505</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>45799</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>45799</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45799</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>45799</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>46283</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45803</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45803</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>45265</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45818</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>45514</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45708</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>44650</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45863</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45863</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45863</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45867</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45574</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>44616</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>45877</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>45877</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>45881</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45373</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>44585</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>45315</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>45296</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>45373</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>45720</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>45880</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>46085</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>

--- a/Översikt AVESTA.xlsx
+++ b/Översikt AVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>46059</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45103</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>44699</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45254</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45240</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>45643</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>44531</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>45257</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44574</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45817</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>45562</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46246</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46059</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44643</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45370</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>46035</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45804</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45628</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>45995</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>46108</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45889</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45758</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>45863</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>45863</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>45961</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>45569</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>46183</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45190</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45243</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>44574</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>46239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>46244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45952</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>45995</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>46056</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>44467</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>44722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44747</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44477</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>44832</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>44575</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>44747</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>44512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>45267</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45497</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>45007</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44734</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44865</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44876</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>45138</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45369</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>45441</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45473</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>45549</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>45447</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>45453</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45370</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>45408</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>44893</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45884</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44840</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>45405</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>45019</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>44998</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45702</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>45238</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45796</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>45796</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>45796</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45796</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>45656</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>45496</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45496</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45967</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45505</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>45799</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>46021</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>46042</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>45799</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>45799</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45560</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45897</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45897</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45897</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45897</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>45897</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>46045</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>46049</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>45903</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>46049</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45799</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>46055</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45910</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>45911</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45803</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45015</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>46062</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45919</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>45922</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44581</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>45803</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>45265</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>46071</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>45264</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>45370</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>45639</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>45929</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>45936</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>45937</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>46013</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>45583</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>45583</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45937</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>45943</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>45902</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>45944</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44739</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>45948</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>45182</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45948</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>45951</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>45453</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>46111</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>44967</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>44972</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>45954</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11747,7 +11747,7 @@
         <v>46113</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>46113</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>46113</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>46113</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>46113</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>46113</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>45123</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>44966</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>45314</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>45800</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45736</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>45602</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>45044</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44971</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>45611</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45446</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>45912</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>46128</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>46128</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>46128</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>46128</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>45457</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>45602</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>45982</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>46133</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>46135</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>45994</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>45455</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>45999</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>46000</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45915</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44855</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>45625</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>45791</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45082</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>45866</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45702</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>45078</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>45818</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45008</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45511</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>44839</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44746</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45729</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45196</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45196</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>45910</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45751</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45232</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>45719</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45721</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>46141</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45492</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>46146</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45009</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45009</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>46146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>44551</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45721</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45763</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45510</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>44684</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45803</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>46134</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>46155</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>44900</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45792</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>46155</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>46155</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>46055</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>45769</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45791</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>45514</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45708</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>44650</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>44980</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45330</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>46169</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>46169</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>46169</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45863</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45269</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45505</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45863</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45863</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>46175</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45867</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45040</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45574</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>46034</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45792</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>44963</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>46124</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45138</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>46183</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>44616</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>46185</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>46184</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45598</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45583</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45008</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>44571</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>46198</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45877</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>46198</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>46196</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45103</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45499</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>46198</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45881</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>46205</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>45649</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45684</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>46252</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45715</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>44613</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44614</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44753</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45231</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45274</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45162</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>46261</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45191</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45266</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45257</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>46223</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44746</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>46265</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>45328</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>46168</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45348</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>45265</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45269</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44875</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>46275</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45496</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45496</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45266</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>46283</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45721</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>46283</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45562</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>46288</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>46244</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>46287</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44739</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45072</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44587</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>46178</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>46246</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45210</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>45527</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>45040</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>45190</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>44687</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>45058</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>45598</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45583</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>45593</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45058</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45316</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45734</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>45583</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45273</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45008</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45007</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>45252</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>44977</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45007</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>44809</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>44508</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45505</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45321</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44971</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45123</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45123</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45646</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>45058</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45694</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45538</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45628</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45777</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45369</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45405</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>45553</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45316</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45510</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45373</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>44585</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45315</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>45296</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>45373</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45720</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>45880</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>46085</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>

--- a/Översikt AVESTA.xlsx
+++ b/Översikt AVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>46059</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45103</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>44699</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45254</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45240</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>45643</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>44531</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>45257</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44574</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45817</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>45562</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46246</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46059</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44643</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45370</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>46035</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45804</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45628</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>45995</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>46108</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45889</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45758</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>45863</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>45863</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>45961</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>45569</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>46183</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45190</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45243</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>44574</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>46239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>46244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45952</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>45995</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>46056</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>44467</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>44643</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>44722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44747</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44477</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>44832</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>44575</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>44747</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>44512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>45267</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45497</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>45007</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44734</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44865</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44876</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>45138</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45369</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>45441</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45473</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>45549</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>45447</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>45453</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45370</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>45408</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>44893</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45884</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44840</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>45405</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>45019</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>44998</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45702</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>45238</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45796</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>45796</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>45796</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45796</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>45656</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>45496</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45496</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45967</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45505</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>45799</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>46021</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>46042</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>45799</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>45799</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45560</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45897</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45897</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45897</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45897</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>45897</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>46045</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>46049</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>45903</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>46049</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45799</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>46055</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45910</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>45911</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45803</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45015</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>46062</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45919</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>45922</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44581</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>45803</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>45265</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>46071</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>45264</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>45370</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>45639</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>45929</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>45936</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>45937</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>46013</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>45583</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>45583</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45937</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>45943</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>45902</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>45944</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44739</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>45948</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>45182</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45948</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>45951</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>45453</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>46111</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>44967</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>44972</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>45954</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11747,7 +11747,7 @@
         <v>46113</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>46113</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>46113</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>46113</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>46113</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>46113</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>45123</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>44966</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>45314</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>45800</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45736</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>45602</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>45044</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44971</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>45611</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45446</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>45912</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>46128</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>46128</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>46128</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>46128</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>45457</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>45602</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>45982</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>46133</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>46135</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>45994</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>45455</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>45999</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>46000</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45915</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44855</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>45625</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>45791</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45082</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>45866</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45702</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>45078</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>45818</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45008</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45511</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>44839</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44746</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45729</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45196</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45196</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>45910</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45751</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45232</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>45719</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45721</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>46141</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45492</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>46146</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45009</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45009</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>46146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>44551</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45721</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45763</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45510</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>44684</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45803</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>46134</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>46155</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>44900</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45792</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>46155</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>46155</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>46055</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>45769</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45791</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>45514</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45708</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>44650</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>44980</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45330</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>46169</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>46169</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>46169</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45863</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45269</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45505</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45863</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45863</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>46175</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45867</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45040</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45574</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>46034</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45792</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>44963</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>46124</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45138</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>46183</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>44616</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>46185</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>46184</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45598</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45583</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45008</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>44571</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>46198</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45877</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>46198</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>46196</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45103</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45499</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>46198</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45881</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>46205</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>45649</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45684</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>46252</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45715</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>44613</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44614</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44753</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45231</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45274</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45162</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>46261</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45191</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45266</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45257</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>46223</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44746</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>46265</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>45328</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>46168</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45348</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>45265</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45269</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>44875</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>46275</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45496</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45496</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45266</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>46283</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45721</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>46283</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45562</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>46288</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>46244</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>46287</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44739</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45072</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44587</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>46178</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>46246</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45210</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>45527</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>45040</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>45190</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>44687</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>45058</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>45598</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45583</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>45593</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45058</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45316</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45734</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>45583</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45273</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45008</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45007</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>45252</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>44977</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45007</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>44809</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>44508</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45505</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45321</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>44971</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45123</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45123</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45646</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>45058</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45694</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45538</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45628</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45777</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45369</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45405</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>45553</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45316</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45510</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45373</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>44585</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45315</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>45296</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>45373</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45720</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>45880</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>46085</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>

--- a/Översikt AVESTA.xlsx
+++ b/Översikt AVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>46059</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45254</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>45103</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44699</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45643</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45257</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45240</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44531</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44574</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45817</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>45562</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46246</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46059</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44643</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45243</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45628</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45995</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>45736</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45889</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46108</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>45370</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45863</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45863</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45758</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>45961</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>46183</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>45569</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45190</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>46239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>46244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>46035</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>44574</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>45952</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>45995</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>46056</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>44643</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44722</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44831</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>44477</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>44832</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>44575</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>44839</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44747</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>44512</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44963</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>45252</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45267</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>45082</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>45510</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>44967</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45265</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45008</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>45123</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45314</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45123</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45019</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>45496</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>45510</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45583</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45583</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>45138</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>44855</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45316</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44571</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>45447</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>45897</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45897</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45897</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45897</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44684</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44614</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45903</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>46021</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45967</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45598</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>45598</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44809</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>45560</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>46042</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44998</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>45910</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>45911</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>46045</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45796</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>45405</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>45238</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>45702</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>45796</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>45796</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>45796</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45269</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>46049</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>46049</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>45656</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>45505</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>45799</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>45799</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>45799</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>45799</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>45803</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>45803</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>45919</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>45265</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>45922</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>46055</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>45751</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>45929</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>45015</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>46062</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>45593</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>45499</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45040</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>45257</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>45936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>45937</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44746</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>46071</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>45937</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>45348</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>45943</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45902</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45944</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>45948</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45948</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>45951</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45058</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44753</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44980</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>45954</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>45496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>45496</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>44972</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>46013</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>45800</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>45583</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>45721</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45912</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>45492</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>45266</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>44865</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>44687</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>45818</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>45982</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>44587</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>46111</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>46113</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>46113</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>46113</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>46113</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>46113</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>45196</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45196</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>46113</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45328</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45446</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45994</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45611</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>46128</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>46128</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>46128</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>46128</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>44746</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45999</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>46000</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45007</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>44508</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>45162</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45684</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>46135</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>46133</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>45527</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45866</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45602</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45370</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45915</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45514</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45511</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>45708</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45008</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45007</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45505</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>44650</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>44971</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45910</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45138</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45721</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45496</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>45457</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>45791</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>45321</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>45044</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45863</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45863</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45863</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>45269</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45867</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44977</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>45628</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>45007</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>45574</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>45729</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>46146</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>46146</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>46134</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45719</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>46155</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45803</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45792</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>46155</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>46155</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45769</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45453</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45791</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>44616</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>46055</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45497</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45694</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45734</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45040</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45370</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>44581</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>46169</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>46169</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>46169</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45715</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>45881</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45441</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45058</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45455</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>46175</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45792</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45072</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>46124</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>46034</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>45330</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19898,7 +19898,7 @@
         <v>45884</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>44876</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45232</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45274</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45649</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45702</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>44839</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>46183</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>46185</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45505</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44551</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>44966</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45210</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>44971</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45182</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>46196</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44893</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>46198</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>46198</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>46198</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44734</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>46205</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>45009</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>45009</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>46265</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>46261</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>46223</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45191</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>46168</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>46275</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44739</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45231</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>44900</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45583</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>45583</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45549</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>46283</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>46283</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>46244</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>46288</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>46287</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>46246</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44613</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45273</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>46178</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45877</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>46184</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>44840</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45266</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45190</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45473</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>45408</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45369</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44875</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>46252</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>46297</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>45008</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>46296</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>46296</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45763</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45316</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45602</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44739</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45538</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45625</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45646</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45264</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45078</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45123</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45562</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45721</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>45103</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45453</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>45639</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>45777</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>45369</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45405</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45553</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45373</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>44585</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>45315</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>45296</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>45373</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>45720</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>45880</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>46085</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>

--- a/Översikt AVESTA.xlsx
+++ b/Översikt AVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>46059</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>46042</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45254</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>45103</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>44699</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45643</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45257</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45240</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>44531</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44574</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45817</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>45562</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46246</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46059</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44643</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45243</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>45628</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45995</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>45736</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45889</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46108</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>45370</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45863</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45863</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45758</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>45961</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>46183</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>45569</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45190</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>45058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>46239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>46244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>46035</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>44574</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>45952</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>45995</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>46056</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>44643</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44722</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44831</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>44477</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>44832</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>44575</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>44839</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44747</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>44512</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44963</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>45252</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45267</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>45082</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>45510</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>44967</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45265</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45008</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>45123</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45314</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45123</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45019</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>45496</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>45510</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45583</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45583</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>45138</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>44855</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45316</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44571</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>45447</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>45897</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45897</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45897</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45897</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44684</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44614</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45903</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>46021</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45967</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45598</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>45598</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44809</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>45560</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>46042</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44998</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>45910</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>45911</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>46045</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45796</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>45405</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>45238</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>45702</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>45796</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>45796</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>45796</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45269</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>46049</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>46049</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>45656</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>45505</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>45799</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>45799</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>45799</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>45799</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>45803</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>45803</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>45919</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>45265</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>45922</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>46055</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>45751</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>45929</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>45015</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>46062</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>45593</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>45499</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45040</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>45257</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>45936</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>45937</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44746</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>46071</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>45937</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>45348</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>45943</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45902</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45944</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>45948</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45948</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>45951</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45058</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44753</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44980</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>45954</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>45496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>45496</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>44972</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>46013</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>45800</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>45583</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>45721</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45912</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>45492</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>45266</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>44865</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>44687</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>45818</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>45982</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>44587</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>46111</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>46113</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>46113</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>46113</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>46113</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>46113</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>45196</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45196</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>46113</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45328</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45446</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45994</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45611</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>46128</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>46128</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>46128</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>46128</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>44746</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45999</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>46000</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45007</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>44508</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>45162</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45684</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>46135</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>46133</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>45527</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45866</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45602</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45370</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45915</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45514</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45511</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>45708</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45008</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45007</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45505</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>44650</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>44971</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45910</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45138</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45721</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45496</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>45457</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>45791</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>45321</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>45044</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45863</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45863</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45863</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>45269</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45867</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44977</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>45628</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>45007</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>45574</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>45729</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>46146</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>46146</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>46134</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45719</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>46155</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45803</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45792</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>46155</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>46155</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45769</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45453</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45791</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>44616</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>46055</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45497</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45694</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45734</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45040</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45370</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>44581</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>46169</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>46169</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>46169</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45715</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>45881</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45441</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45058</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45455</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>46175</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45792</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45072</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>46124</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>46034</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>45330</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19898,7 +19898,7 @@
         <v>45884</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>44876</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45232</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45274</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45649</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45702</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>44839</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>46183</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>46185</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45505</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44551</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>44966</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45210</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>44971</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45182</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>46196</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44893</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>46198</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>46198</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>46198</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44734</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>46205</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>45009</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>45009</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>46265</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>46261</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>46223</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45191</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>46168</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>46275</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44739</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45231</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>44900</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45583</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>45583</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45549</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>46283</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>46283</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>46244</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>46288</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>46287</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>46246</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44613</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45273</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>46178</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45877</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>46184</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>44840</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45266</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45190</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45473</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>45408</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>45369</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>44875</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>46252</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>46297</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>45008</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>46296</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>46296</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45763</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45316</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45602</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44739</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45538</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45625</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45646</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45264</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45078</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45123</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45562</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45721</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>45103</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45453</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>45639</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>45777</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>45369</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45405</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45553</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45373</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>44585</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>45315</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>45296</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>45373</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>45720</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>45880</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>46085</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>

--- a/Översikt AVESTA.xlsx
+++ b/Översikt AVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>46059</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45103</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>44699</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45254</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46301</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45240</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>45643</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45257</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>44531</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45562</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>45817</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46246</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>46059</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>44643</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>45370</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>45569</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45804</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>45736</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>45889</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>45190</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45758</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>45863</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>45863</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>45243</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>44574</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>46108</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45058</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>45628</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45995</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>45961</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>46183</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>46239</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>46035</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45952</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>45995</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>46056</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44643</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44722</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44831</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44747</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44512</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44575</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44839</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44832</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44747</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>45763</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44865</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>45510</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45138</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44684</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>45369</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>44876</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>45007</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45583</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>45441</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44900</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>45593</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>45058</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>45316</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45267</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>45497</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45734</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>45447</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>45473</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45549</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>45453</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>45583</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>45408</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45370</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>45273</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44734</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44980</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>45281</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>45008</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45007</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>45252</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>44893</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>44977</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>45884</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45007</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>44809</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44840</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44508</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>45505</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45330</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>45019</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45321</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>44971</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>45123</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>45123</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45646</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>45269</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>45058</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>45505</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>45496</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>45496</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>45897</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45897</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45897</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45897</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>45694</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>45538</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>45628</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>45903</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>45040</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>45560</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44963</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>45910</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>45777</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45911</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45138</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45369</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>45405</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>45598</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45583</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45919</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45553</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>45922</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>45316</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>44581</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45510</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>45264</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>45370</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>45008</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>44571</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45639</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45929</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45405</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45103</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>44998</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>45702</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45238</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45796</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45499</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45796</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45796</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45796</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45656</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45936</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45505</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45799</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>45799</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>45799</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>45583</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45583</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45799</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>45803</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>45649</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>45684</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>45803</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>45265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45715</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>44739</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>45937</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45937</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>45182</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45943</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45902</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>44613</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>45453</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>45944</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>44967</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>45123</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44966</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>45818</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>45314</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45948</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45948</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>44614</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45602</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45044</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44971</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>44753</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45951</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45611</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>45446</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45231</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>44972</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45954</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45274</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45162</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45800</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45457</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45602</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45191</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45912</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45514</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>45266</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>45257</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45708</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>44650</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>44746</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45455</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>45328</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>44855</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>45863</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>45625</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45863</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>45863</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>45867</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>45082</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>45702</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>45574</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>45078</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>44616</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45008</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45348</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44839</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44746</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45729</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>45265</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45982</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>45269</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45196</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>44875</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>45196</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45881</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45496</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>45496</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>45751</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>45232</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>45719</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45721</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>45266</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>45492</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>46111</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>46113</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>45009</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>45009</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>46113</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>46113</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>46113</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45721</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>46113</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>46113</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>44551</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45994</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45721</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45999</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>46000</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45562</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>46128</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>46128</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>46128</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>46128</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>46133</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44739</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45072</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>44587</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>46135</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>45915</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>45210</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45791</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>45527</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45866</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45967</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>45040</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>46021</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45511</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>46042</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>45190</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>44687</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>45598</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>45910</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>46045</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>46049</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>46049</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>46055</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45015</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>46146</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>46062</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>46146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>46071</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45803</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>46134</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>46155</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45792</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>46155</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>46155</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>46055</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45769</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>46013</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45791</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>46169</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>46169</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>46169</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>46175</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>46034</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45792</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>46124</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>46183</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>46185</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>46198</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>46198</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>46196</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>46198</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>46223</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>46265</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>46168</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>46275</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>46283</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>46283</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>46288</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>46244</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>46287</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>46178</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>46246</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>46184</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>45877</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>46296</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>46296</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>46297</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>46252</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>46301</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>46301</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>46301</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>46303</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>46261</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>46205</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>45373</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44585</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45315</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45296</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45373</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45720</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45880</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>46085</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>

--- a/Översikt AVESTA.xlsx
+++ b/Översikt AVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>46059</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45103</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>44699</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45254</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46301</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45240</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>45643</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45257</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>44531</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45562</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>45817</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46246</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>46059</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>44643</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>45370</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>45569</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45804</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>45736</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>45889</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>45190</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45758</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>45863</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>45863</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>45243</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>44574</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>46108</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45058</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>45628</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45995</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>45961</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>46183</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>46239</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>46244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>46035</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45952</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>45995</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>46056</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44643</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44722</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44831</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44747</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44512</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44575</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44839</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44832</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44747</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>45763</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44865</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>45510</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45138</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44684</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>45369</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>44876</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>45007</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45583</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>45441</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44900</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>45593</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>45058</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>45316</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45267</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>45497</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45734</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>45447</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>45473</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45549</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>45453</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>45583</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>45408</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45370</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>45273</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44734</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44980</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>45281</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>45008</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45007</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>45252</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>44893</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>44977</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>45884</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45007</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>44809</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44840</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44508</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>45505</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45330</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>45019</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45321</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>44971</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>45123</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>45123</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45646</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>45269</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>45058</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>45505</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>45496</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>45496</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>45897</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45897</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45897</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45897</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>45694</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>45538</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>45628</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>45903</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>45040</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
         <v>45560</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44963</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>45910</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>45777</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45911</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45138</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45369</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>45405</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>45598</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45583</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45919</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45553</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>45922</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>45316</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>44581</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45510</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>45264</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>45370</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>45008</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>44571</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45639</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45929</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45405</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45103</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>44998</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>45702</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45238</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45796</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45499</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45796</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45796</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45796</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45656</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45936</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45505</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45799</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>45799</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>45799</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>45583</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45583</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45799</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>45803</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>45649</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>45684</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>45803</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>45265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45715</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>44739</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>45937</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45937</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>45182</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45943</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45902</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>44613</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>45453</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>45944</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>44967</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>45123</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44966</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>45818</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>45314</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45948</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45948</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>44614</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45602</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45044</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44971</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>44753</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45951</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45611</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>45446</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45231</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>44972</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45954</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>45274</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45162</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45800</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45457</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45602</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45191</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45912</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45514</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>45266</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>45257</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45708</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>44650</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>44746</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45455</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>45328</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>44855</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>45863</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>45625</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45863</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>45863</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>45867</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>45082</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>45702</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>45574</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>45078</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>44616</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45008</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45348</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44839</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44746</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45729</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>45265</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45982</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>45269</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45196</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>44875</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>45196</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45881</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45496</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>45496</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>45751</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>45232</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>45719</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45721</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>45266</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18968,7 +18968,7 @@
         <v>45492</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>46111</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>46113</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>45009</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>45009</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>46113</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>46113</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>46113</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45721</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>46113</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>46113</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>44551</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45994</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45721</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45999</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>46000</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45562</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>46128</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>46128</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>46128</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>46128</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>46133</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44739</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45072</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>44587</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>46135</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>45915</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>45210</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45791</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>45527</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45866</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45967</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>45040</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>46021</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45511</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>46042</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>45190</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>44687</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>45598</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>45910</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>46045</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>46049</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>46049</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>46055</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45015</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>46146</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>46062</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>46146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>46071</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45803</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>46134</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>46155</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45792</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>46155</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>46155</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>46055</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45769</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>46013</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45791</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>46169</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>46169</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>46169</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>46175</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>46034</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45792</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>46124</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>46183</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>46185</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>46198</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>46198</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>46196</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>46198</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>46223</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>46265</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>46168</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>46275</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>46283</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>46283</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>46288</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>46244</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>46287</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>46178</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>46246</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>46184</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>45877</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>46296</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>46296</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>46297</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>46252</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>46301</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>46301</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>46301</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>46303</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>46261</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>46205</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>45373</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44585</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45315</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45296</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45373</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45720</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45880</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>46085</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>

--- a/Översikt AVESTA.xlsx
+++ b/Översikt AVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>46059</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45254</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45103</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44699</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>46042</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46301</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45257</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45240</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44531</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45643</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45562</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46246</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46309</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45817</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>46059</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44643</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45243</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45370</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>45736</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>45889</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45961</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>45628</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>45995</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>45569</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>46108</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>46183</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>45190</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45058</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>46239</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>46244</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>46035</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44574</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>45804</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>45863</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>45863</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>45758</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>45952</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>45995</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>46056</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>44643</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>44722</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>44747</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>44832</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44839</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44575</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44747</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45252</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44963</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45267</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45082</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>44967</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>45510</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>45008</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>45265</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>45123</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>45123</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>45314</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45496</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>45583</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45583</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44855</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45138</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>45447</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44684</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44614</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44809</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45598</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>45598</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>45560</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>45019</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>45269</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>45751</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>45040</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45257</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44746</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>45593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>45348</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44753</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>45058</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>45496</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>45496</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>44980</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45721</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>45492</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>45583</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44865</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>44687</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44587</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>45499</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45915</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45196</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>45196</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>45328</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>45511</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>45446</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>45910</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>45611</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>44746</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45884</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45007</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44508</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45897</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>45897</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45162</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45897</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>45897</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>45684</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45791</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>45903</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>45527</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>45602</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>45370</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>45910</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>45911</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>46146</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>46146</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>45919</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45922</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>45008</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>45007</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45505</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45929</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>44971</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>45936</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>45138</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>45937</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>45721</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45937</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>45496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45457</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45943</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45902</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>45944</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>46134</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45321</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>45044</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>45948</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>45948</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45951</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>46155</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45803</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45792</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45269</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>46155</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>46155</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>45954</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>44972</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45769</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>44977</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>45628</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45007</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>45791</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45800</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>45729</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>46055</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>45912</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45982</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45719</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>45453</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>45497</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>46169</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>46169</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45994</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45694</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>45734</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45040</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45370</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>46169</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45999</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>46000</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>44581</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45715</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>45441</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45058</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45455</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45072</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45330</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>44876</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>45232</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45274</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>46175</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45649</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45702</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>44839</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>46021</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>45967</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45792</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>46124</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>46034</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>46042</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>46045</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>46049</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>46049</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45505</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44551</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>44966</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46055</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45210</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>44971</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45182</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44893</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>45015</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>46062</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>46183</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>46071</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>44734</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>46185</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45009</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45009</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>46013</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>46196</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>46198</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>46198</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>46111</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>46198</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>46113</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>46113</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>46113</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>46113</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>46113</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>46113</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>45191</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>46128</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>46128</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>46128</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>46128</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>46135</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>46133</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>44739</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45866</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>45231</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>44900</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45583</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45583</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45549</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>46223</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44613</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45273</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>46168</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46275</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>44840</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45266</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45190</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>45473</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45408</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45369</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>44875</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45008</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>46283</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>46283</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>45763</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45316</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>46244</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45602</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>46288</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>46287</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>44739</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45538</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>46246</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45625</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>46178</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45646</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45877</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45264</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>46184</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45078</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45123</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45562</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>45721</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45103</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>46252</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45453</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>46297</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>46296</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>46296</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45639</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>46301</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>46301</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45777</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45369</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45405</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45553</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>46303</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>46301</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>45510</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45316</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>46261</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44998</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>46307</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>45796</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45405</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45238</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45702</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>45796</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45796</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45796</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>46307</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>46307</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>45656</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45505</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>46205</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45799</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>45799</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45799</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>46307</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>45799</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>45803</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45803</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>46265</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>45265</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>46309</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>46311</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45818</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>45514</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>45708</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>44650</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>45863</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>45863</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45863</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>45867</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45574</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44616</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45881</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45373</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>44585</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>45315</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45296</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45373</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>45720</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45880</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>46085</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>

--- a/Översikt AVESTA.xlsx
+++ b/Översikt AVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>46059</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45254</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45103</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>44699</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>46042</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46301</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45257</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45240</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44531</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45643</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45562</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>46246</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46309</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45817</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>46059</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44643</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45243</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45370</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>45736</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>45889</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45961</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>45628</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>45995</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>45569</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>46108</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>46183</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>45190</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45058</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>46239</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>46244</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>46035</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44574</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>45804</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>45863</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>45863</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>45758</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>45952</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>45995</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>46056</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>44643</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>44722</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>44747</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>44832</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44839</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44575</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44747</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45252</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44963</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45267</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45082</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>44967</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>45510</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>45008</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>45265</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>45123</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>45123</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>45314</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45496</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>45583</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45583</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>44855</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45138</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>45447</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44684</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44614</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44809</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45598</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>45598</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>45560</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>45019</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>45269</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>45751</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>45040</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45257</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44746</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>45593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>45348</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44753</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>45058</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>45496</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>45496</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>44980</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45721</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>45492</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>45583</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44865</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>44687</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44587</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>45499</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45915</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45196</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>45196</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>45328</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>45511</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>45446</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>45910</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>45611</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>44746</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45884</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45007</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44508</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45897</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>45897</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45162</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45897</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>45897</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>45684</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45791</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>45903</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>45527</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>45602</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>45370</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>45910</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>45911</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>46146</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>46146</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>45919</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45922</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>45008</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>45007</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45505</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45929</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>44971</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>45936</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>45138</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>45937</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>45721</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45937</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>45496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45457</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45943</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45902</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>45944</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>46134</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45321</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>45044</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>45948</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>45948</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45951</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>46155</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45803</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45792</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45269</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>46155</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>46155</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>45954</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>44972</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45769</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>44977</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>45628</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45007</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>45791</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45800</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>45729</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>46055</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>45912</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45982</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45719</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>45453</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>45497</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>46169</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>46169</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45994</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45694</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>45734</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45040</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45370</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>46169</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45999</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>46000</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>44581</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45715</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>45441</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45058</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45455</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45072</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45330</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>44876</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>45232</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45274</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>46175</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45649</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45702</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>44839</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>46021</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>45967</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45792</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>46124</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>46034</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>46042</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>46045</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>46049</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>46049</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45505</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44551</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>44966</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46055</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45210</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>44971</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45182</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44893</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>45015</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>46062</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>46183</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>46071</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>44734</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>46185</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45009</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45009</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>46013</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>46196</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>46198</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>46198</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>46111</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>46198</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>46113</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>46113</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>46113</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>46113</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>46113</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>46113</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>45191</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>46128</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>46128</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>46128</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>46128</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>46135</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>46133</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>44739</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45866</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>45231</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>44900</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45583</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45583</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45549</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>46223</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44613</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45273</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>46168</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>46275</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>44840</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45266</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45190</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>45473</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45408</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45369</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>44875</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45008</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>46283</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>46283</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>45763</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45316</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>46244</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45602</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>46288</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>46287</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>44739</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45538</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>46246</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45625</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>46178</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45646</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45877</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45264</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>46184</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45078</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45123</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45562</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>45721</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45103</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>46252</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45453</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>46297</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>46296</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>46296</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45639</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>46301</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>46301</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45777</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45369</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45405</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45553</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>46303</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>46301</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>45510</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45316</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>46261</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44998</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>46307</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>45796</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45405</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45238</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45702</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>45796</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45796</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45796</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>46307</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>46307</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>45656</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45505</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>46205</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45799</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>45799</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45799</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>46307</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>45799</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>45803</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45803</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>46265</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>45265</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>46309</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>46311</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45818</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>45514</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>45708</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>44650</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>45863</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>45863</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45863</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>45867</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45574</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44616</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45881</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45373</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>44585</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>45315</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45296</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45373</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>45720</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45880</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>46085</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>

--- a/Översikt AVESTA.xlsx
+++ b/Översikt AVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>46059</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45254</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>46042</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46301</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45103</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>44699</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45643</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45240</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44531</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45257</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45817</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>44574</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>46246</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>46309</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45562</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>46059</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44643</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45058</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45370</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45961</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>45736</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45889</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>46183</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>46244</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45804</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>46035</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>45628</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>45995</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>46108</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>45758</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45863</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>45863</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>45569</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45190</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>45243</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>44574</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>45952</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>45995</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>46056</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>44643</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>44722</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>44747</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>44832</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44575</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44839</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44747</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>44739</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>45007</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45267</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45497</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>45072</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>45884</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>44587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>45897</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>45897</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45897</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45897</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44734</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44865</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>45903</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>45769</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>45210</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>45910</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>45527</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>45911</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>45791</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>45040</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45919</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>45922</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>45190</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44687</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>45598</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>46169</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>45138</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>46169</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>46169</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>45369</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>45929</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>44876</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45936</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>45937</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45937</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>46175</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>45943</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>45441</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45902</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>45447</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45473</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45549</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45453</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>45408</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>45944</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>45370</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>46034</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>45792</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>45583</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>45948</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>45948</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>46124</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>45593</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>45951</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>45058</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>45316</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>46183</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>45734</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44972</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>45954</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>46185</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>45583</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>45800</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>45273</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>45912</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45008</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>45007</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>46198</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>45252</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44977</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>46198</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>46196</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45007</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44809</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>44508</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>45505</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>46198</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>45281</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45321</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>44971</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45123</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45123</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45646</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45982</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>44893</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>45694</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>45994</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45538</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>45628</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>44840</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>45999</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>46000</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>46223</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>45777</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>46168</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>45369</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>45405</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>45553</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45316</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>45510</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>46283</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45967</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45019</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>46283</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>46021</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45405</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>44998</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>45702</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>46042</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>46288</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45238</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45796</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>46244</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>45796</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>45796</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>45796</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45656</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>46287</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>45505</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>46045</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>45799</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>46049</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45799</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45799</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>45799</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>46049</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>45803</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45803</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45265</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>46055</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>46178</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>46246</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>45015</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>46062</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>46184</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>45818</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>45877</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>46071</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>46296</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>46296</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>46013</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>46297</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45496</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45496</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45514</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>46252</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45708</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44650</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>46301</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>46301</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>46301</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>46111</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>46113</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>46113</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>46113</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>46113</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>46303</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>45863</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>46113</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>46113</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>45863</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>45863</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>45867</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>45574</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>44616</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>46261</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>46205</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>46128</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>46307</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>46265</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>46128</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>46128</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>46128</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45881</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>45560</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>46133</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>46307</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>46307</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>46307</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>46309</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>46135</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>46311</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45915</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45791</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>45866</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>44581</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>45370</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45511</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45639</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45910</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45583</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45583</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>46146</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>46146</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>46275</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44739</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45803</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>46134</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45182</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>46155</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45453</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>45792</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>44967</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>46155</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>46155</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45123</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>46055</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44966</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45314</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45602</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45044</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>44971</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45611</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>45446</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45457</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45602</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>45455</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44855</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45625</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45082</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45702</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>45078</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45008</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44839</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>44746</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45729</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45196</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45196</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45751</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>45232</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>45719</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>45721</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>45492</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45009</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45009</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44551</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45721</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45763</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45510</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>44684</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>44900</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>44980</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>45330</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45269</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45505</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45040</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>44963</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>45138</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45598</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45583</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45008</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>44571</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45103</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>45499</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>45649</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>45684</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45715</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44613</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>44614</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44753</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>45231</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>45274</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45162</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45191</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45266</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>45257</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>44746</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45328</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>45348</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>45265</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45269</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>44875</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>45496</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>45496</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>45266</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>45721</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>45562</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45373</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>44585</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45315</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>45296</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45373</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45720</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45880</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>46085</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>

--- a/Översikt AVESTA.xlsx
+++ b/Översikt AVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45834</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>46059</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45254</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>46042</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46301</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45103</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>44699</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45643</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45240</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44531</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45257</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45817</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>44574</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>46246</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>46309</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45562</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>46059</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>44643</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45058</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45370</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45961</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>45736</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45889</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>46183</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>46239</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>46244</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45804</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>46035</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>45628</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>45995</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>46108</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>45758</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45863</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>45863</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>45569</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45190</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>45243</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>44574</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>45952</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>45995</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>46056</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>44643</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>44722</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>44747</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>44832</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44575</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>44839</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44747</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>44739</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>45007</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>45267</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45497</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>45072</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>45884</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>44587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>45897</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>45897</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45897</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45897</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44734</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44865</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>45903</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>45769</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>45210</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>45910</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>45527</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>45911</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>45791</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>45040</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>45919</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>45922</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>45190</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44687</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>45598</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>46169</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>45138</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>46169</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>46169</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>45369</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>45929</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>44876</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45936</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>45937</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45937</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>46175</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>45943</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>45441</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45902</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>45447</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45473</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45549</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45453</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>45408</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>45944</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>45370</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>46034</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>45792</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>45583</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>45948</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>45948</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>46124</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>45593</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>45951</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>45058</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>45316</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>46183</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>45734</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44972</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>45954</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>46185</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>45583</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>45800</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>45273</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>45912</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45008</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>45007</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>46198</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>45252</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44977</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>46198</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>46196</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45007</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44809</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>44508</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>45505</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>46198</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>45281</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45321</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>44971</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45123</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45123</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45646</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45982</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45058</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>44893</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>45694</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>45994</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45538</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>45628</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>44840</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>45999</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>46000</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>46223</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>45777</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>46168</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>45369</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>45405</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>45553</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45316</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>45510</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>46283</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45967</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45019</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>46283</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>46021</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45405</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>44998</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>45702</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>46042</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>46288</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45238</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45796</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>46244</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>45796</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>45796</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>45796</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45656</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>46287</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>45505</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>46045</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>45799</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>46049</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45799</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45799</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>45799</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>46049</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>45803</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45803</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45265</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>46055</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>46178</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>46246</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>45015</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>46062</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>46184</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>45818</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>45877</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>46071</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>46296</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>46296</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>46013</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>46297</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45496</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45496</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45514</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>46252</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45708</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44650</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>46301</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>46301</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>46301</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>46111</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>46113</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>46113</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>46113</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>46113</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>46303</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>45863</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>46113</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>46113</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>45863</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>45863</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>45867</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>45574</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>44616</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>46261</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>46205</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>46128</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>46307</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>46265</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>46128</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>46128</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>46128</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45881</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>45560</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>46133</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>46307</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>46307</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>46307</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>46309</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>46135</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>46311</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45915</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45791</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>45866</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>44581</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>45370</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45511</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45639</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45910</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45583</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45583</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>46146</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>46146</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>46275</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44739</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45803</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>46134</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45182</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>46155</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45453</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>45792</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>44967</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>46155</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>46155</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45123</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>46055</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44966</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45314</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45602</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45044</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>44971</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45611</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>45446</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45457</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45602</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>45455</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44855</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45625</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45082</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45702</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>45078</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45008</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44839</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>44746</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45729</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45196</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45196</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45751</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>45232</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>45719</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>45721</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>45492</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45009</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45009</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44551</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45721</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45763</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45510</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>44684</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>44900</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>44980</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>45330</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45269</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45505</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45040</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>44963</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>45138</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45598</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45583</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45008</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>44571</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45103</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>45499</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>45649</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>45684</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45715</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44613</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>44614</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44753</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>45231</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>45274</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45162</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45191</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45266</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>45257</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>44746</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45328</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>45348</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>45265</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45269</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>44875</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>45496</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>45496</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>45266</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>45721</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>45562</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45373</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>44585</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45315</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>45296</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45373</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45720</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45880</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>46085</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
